--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2022.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:16</t>
+    <t xml:space="preserve">2026-09-09 21:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2022.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:00</t>
+    <t xml:space="preserve">2026-09-17 13:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2022.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:48</t>
+    <t xml:space="preserve">2026-10-05 18:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1271792.12</v>
+        <v>1271792.13</v>
       </c>
     </row>
     <row r="3">
@@ -546,7 +546,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>944701.12</v>
+        <v>944701.13</v>
       </c>
     </row>
     <row r="10">
@@ -610,7 +610,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>857550.12</v>
+        <v>857550.13</v>
       </c>
     </row>
   </sheetData>
